--- a/site/Dayforce-Greenhouse-Event-Based-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Greenhouse-Event-Based-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>User Management</t>
+          <t>Sensitive Fields</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,129 +671,129 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KKGR0E1X4WS9VGW91EW6JMB7</t>
+          <t>h_01KKGR0E1X2J8YA1DX900C9W7D</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KKGR0E1X4WS9VGW91EW6JMB7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KKGR0E1X2J8YA1DX900C9W7D</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>User Provisioning Settings</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>01KF2ST6Y7GH70E2MJCYT5X2DZ</t>
+          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#01KF2ST6Y7GH70E2MJCYT5X2DZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sensitive Fields</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KKGR0E1X2J8YA1DX900C9W7D</t>
+          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KKGR0E1X2J8YA1DX900C9W7D</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>Successful Integration Notification Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KGPAMEAW2HCGNSBF99C8ADNF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Failed Integration Notification Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#01K5TY1G8QTYYA129P3KWESN2C</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Notification Settings</t>
+          <t>Skipped Integration Notification Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#01K5TY2F66RQRGHM0D3B23C2S3</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,142 +803,120 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K9750G1WVCA080W3BF2A4RY4</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01K9750G1WVCA080W3BF2A4RY4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Successful Integration Notification Settings</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Failed Integration Notification Settings</t>
+          <t>Candidate Configuration</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Candidate Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>h_01KP5CE7FF276MAFECVTT2A1DN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KP5CE7FF276MAFECVTT2A1DN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KQRYSBQN0HXWEP20VS4XDPFD</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KQRYSBQN0HXWEP20VS4XDPFD</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dayforce-Greenhouse-Event-Based-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Greenhouse-Event-Based-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,29 +705,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Notification Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>h_01KRDXWM2EN0GY8QKCSWWP3ZQZ</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KRDXWM2EN0GY8QKCSWWP3ZQZ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Successful Integration Notification Settings</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Failed Integration Notification Settings</t>
+          <t>Successful Integration Notification Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#01KFD1AMVYPNY4PY2ZB7A64VGC</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Skipped Integration Notification Settings</t>
+          <t>Failed Integration Notification Settings</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+          <t>h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KFG2ZYY71TZZJY19NF3Q5K5S</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Skipped Integration Notification Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,63 +803,63 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KPMSJ4R07ANJZ3N7XKKR5WQ1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#01K5X7TJQR0KMMYYXZF7N7W9SG</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Candidate Configuration</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Candidate Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KP5CE7FF276MAFECVTT2A1DN</t>
+          <t>h_01KRDXWM2EG33CBM54TMB99A3W</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KP5CE7FF276MAFECVTT2A1DN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KRDXWM2EG33CBM54TMB99A3W</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Candidate Configuration</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,32 +891,76 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KQRYSBQN0HXWEP20VS4XDPFD</t>
+          <t>h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KQRYSBQN0HXWEP20VS4XDPFD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01JVP6WJ681AK5EKZYA0EHHYMZ</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Candidate Settings</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KP5CE7FF276MAFECVTT2A1DN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KP5CE7FF276MAFECVTT2A1DN</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KQRYSBQN0HXWEP20VS4XDPFD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KQRYSBQN0HXWEP20VS4XDPFD</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Dayforce-Greenhouse-Event-Based-Integration-Guide/headings.xlsx
+++ b/site/Dayforce-Greenhouse-Event-Based-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,7 +837,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Log Insight Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>h_01KRDXWM2EG33CBM54TMB99A3W</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KRDXWM2EG33CBM54TMB99A3W</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Analytics Settings</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KRDXWM2EG33CBM54TMB99A3W</t>
+          <t>01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KRDXWM2EG33CBM54TMB99A3W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#01KAB4M2RSH1S3C6QGA5KJ5HRH</t>
         </is>
       </c>
     </row>
@@ -963,6 +963,28 @@
       <c r="D25" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Update the Integration to the Latest Version</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Dayforce-Greenhouse-Event-Based-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
     </row>
